--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_o_higgins.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>12.89</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>11.13</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>10.34</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>10</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>9.51</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>9.09</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>9.039999999999999</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>8.869999999999999</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>8.85</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>8.619999999999999</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>8.56</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>8.35</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>8.23</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>8.130000000000001</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -578,9 +531,6 @@
       <c r="B16">
         <v>7.69</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -591,9 +541,6 @@
       <c r="B17">
         <v>7.6</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,9 +551,6 @@
       <c r="B18">
         <v>7.32</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -617,9 +561,6 @@
       <c r="B19">
         <v>7.29</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -630,9 +571,6 @@
       <c r="B20">
         <v>7.26</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,9 +581,6 @@
       <c r="B21">
         <v>7.19</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -656,9 +591,6 @@
       <c r="B22">
         <v>7.16</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -669,9 +601,6 @@
       <c r="B23">
         <v>7.13</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -682,9 +611,6 @@
       <c r="B24">
         <v>6.74</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -695,9 +621,6 @@
       <c r="B25">
         <v>6.61</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -708,9 +631,6 @@
       <c r="B26">
         <v>6.2</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -721,9 +641,6 @@
       <c r="B27">
         <v>5.81</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -734,9 +651,6 @@
       <c r="B28">
         <v>5.73</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -747,9 +661,6 @@
       <c r="B29">
         <v>5.43</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -760,9 +671,6 @@
       <c r="B30">
         <v>5.29</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -773,9 +681,6 @@
       <c r="B31">
         <v>4.99</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -786,9 +691,6 @@
       <c r="B32">
         <v>4.91</v>
       </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -799,9 +701,6 @@
       <c r="B33">
         <v>4.36</v>
       </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -811,9 +710,6 @@
       </c>
       <c r="B34">
         <v>3.21</v>
-      </c>
-      <c r="F34" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_o_higgins.xlsx
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>12.89</v>
       </c>
+      <c r="C2">
+        <v>13.05</v>
+      </c>
+      <c r="D2">
+        <v>-0.1600000000000001</v>
+      </c>
+      <c r="E2">
+        <v>-1.226053639846747</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>11.13</v>
       </c>
+      <c r="C3">
+        <v>11.2</v>
+      </c>
+      <c r="D3">
+        <v>-0.06999999999999851</v>
+      </c>
+      <c r="E3">
+        <v>-0.6249999999999867</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>10.34</v>
       </c>
+      <c r="C4">
+        <v>11.14</v>
+      </c>
+      <c r="D4">
+        <v>-0.8000000000000007</v>
+      </c>
+      <c r="E4">
+        <v>-7.181328545780974</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,216 +448,414 @@
       <c r="B5">
         <v>10</v>
       </c>
+      <c r="C5">
+        <v>10.96</v>
+      </c>
+      <c r="D5">
+        <v>-0.9600000000000009</v>
+      </c>
+      <c r="E5">
+        <v>-8.759124087591253</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marchihue</t>
+          <t>Palmilla</t>
         </is>
       </c>
       <c r="B6">
-        <v>9.51</v>
+        <v>9.09</v>
+      </c>
+      <c r="C6">
+        <v>8.91</v>
+      </c>
+      <c r="D6">
+        <v>0.1799999999999997</v>
+      </c>
+      <c r="E6">
+        <v>2.020202020202011</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Palmilla</t>
+          <t>Las Cabras</t>
         </is>
       </c>
       <c r="B7">
-        <v>9.09</v>
+        <v>9.039999999999999</v>
+      </c>
+      <c r="C7">
+        <v>9.74</v>
+      </c>
+      <c r="D7">
+        <v>-0.7000000000000011</v>
+      </c>
+      <c r="E7">
+        <v>-7.186858316221779</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Las Cabras</t>
+          <t>Chépica</t>
         </is>
       </c>
       <c r="B8">
-        <v>9.039999999999999</v>
+        <v>8.869999999999999</v>
+      </c>
+      <c r="C8">
+        <v>8.69</v>
+      </c>
+      <c r="D8">
+        <v>0.1799999999999997</v>
+      </c>
+      <c r="E8">
+        <v>2.071346375143834</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chépica</t>
+          <t>Paredones</t>
         </is>
       </c>
       <c r="B9">
-        <v>8.869999999999999</v>
+        <v>8.85</v>
+      </c>
+      <c r="C9">
+        <v>8.84</v>
+      </c>
+      <c r="D9">
+        <v>0.009999999999999787</v>
+      </c>
+      <c r="E9">
+        <v>0.113122171945701</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paredones</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="B10">
-        <v>8.85</v>
+        <v>8.619999999999999</v>
+      </c>
+      <c r="C10">
+        <v>9.33</v>
+      </c>
+      <c r="D10">
+        <v>-0.7100000000000009</v>
+      </c>
+      <c r="E10">
+        <v>-7.609860664523049</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="B11">
-        <v>8.619999999999999</v>
+        <v>8.56</v>
+      </c>
+      <c r="C11">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="D11">
+        <v>-0.4000000000000004</v>
+      </c>
+      <c r="E11">
+        <v>-4.464285714285721</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="B12">
-        <v>8.56</v>
+        <v>8.35</v>
+      </c>
+      <c r="C12">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="D12">
+        <v>0.0600000000000005</v>
+      </c>
+      <c r="E12">
+        <v>0.7237635705669598</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>La Estrella</t>
         </is>
       </c>
       <c r="B13">
-        <v>8.35</v>
+        <v>8.23</v>
+      </c>
+      <c r="C13">
+        <v>8.93</v>
+      </c>
+      <c r="D13">
+        <v>-0.6999999999999993</v>
+      </c>
+      <c r="E13">
+        <v>-7.838745800671887</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>La Estrella</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="B14">
-        <v>8.23</v>
+        <v>8.130000000000001</v>
+      </c>
+      <c r="C14">
+        <v>8.359999999999999</v>
+      </c>
+      <c r="D14">
+        <v>-0.2299999999999986</v>
+      </c>
+      <c r="E14">
+        <v>-2.751196172248793</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>Quinta de Tilcoco</t>
         </is>
       </c>
       <c r="B15">
-        <v>8.130000000000001</v>
+        <v>7.69</v>
+      </c>
+      <c r="C15">
+        <v>7.4</v>
+      </c>
+      <c r="D15">
+        <v>0.29</v>
+      </c>
+      <c r="E15">
+        <v>3.918918918918912</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
+          <t>Chimbarongo</t>
         </is>
       </c>
       <c r="B16">
-        <v>7.69</v>
+        <v>7.6</v>
+      </c>
+      <c r="C16">
+        <v>7.58</v>
+      </c>
+      <c r="D16">
+        <v>0.01999999999999957</v>
+      </c>
+      <c r="E16">
+        <v>0.2638522427440559</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Chimbarongo</t>
+          <t>Malloa</t>
         </is>
       </c>
       <c r="B17">
-        <v>7.6</v>
+        <v>7.32</v>
+      </c>
+      <c r="C17">
+        <v>8.02</v>
+      </c>
+      <c r="D17">
+        <v>-0.6999999999999993</v>
+      </c>
+      <c r="E17">
+        <v>-8.728179551122183</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Malloa</t>
+          <t>Peralillo</t>
         </is>
       </c>
       <c r="B18">
-        <v>7.32</v>
+        <v>7.29</v>
+      </c>
+      <c r="C18">
+        <v>7.82</v>
+      </c>
+      <c r="D18">
+        <v>-0.5300000000000002</v>
+      </c>
+      <c r="E18">
+        <v>-6.777493606138107</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Peralillo</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="B19">
-        <v>7.29</v>
+        <v>7.26</v>
+      </c>
+      <c r="C19">
+        <v>7.96</v>
+      </c>
+      <c r="D19">
+        <v>-0.7000000000000002</v>
+      </c>
+      <c r="E19">
+        <v>-8.793969849246231</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Olivar</t>
         </is>
       </c>
       <c r="B20">
-        <v>7.26</v>
+        <v>7.19</v>
+      </c>
+      <c r="C20">
+        <v>7.14</v>
+      </c>
+      <c r="D20">
+        <v>0.05000000000000071</v>
+      </c>
+      <c r="E20">
+        <v>0.7002801120448376</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Olivar</t>
+          <t>Navidad</t>
         </is>
       </c>
       <c r="B21">
-        <v>7.19</v>
+        <v>7.16</v>
+      </c>
+      <c r="C21">
+        <v>6.27</v>
+      </c>
+      <c r="D21">
+        <v>0.8900000000000006</v>
+      </c>
+      <c r="E21">
+        <v>14.19457735247209</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Navidad</t>
+          <t>Pumanque</t>
         </is>
       </c>
       <c r="B22">
-        <v>7.16</v>
+        <v>7.13</v>
+      </c>
+      <c r="C22">
+        <v>6.85</v>
+      </c>
+      <c r="D22">
+        <v>0.2800000000000002</v>
+      </c>
+      <c r="E22">
+        <v>4.087591240875921</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pumanque</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="B23">
-        <v>7.13</v>
+        <v>6.74</v>
+      </c>
+      <c r="C23">
+        <v>6.64</v>
+      </c>
+      <c r="D23">
+        <v>0.1000000000000005</v>
+      </c>
+      <c r="E23">
+        <v>1.506024096385561</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>Requínoa</t>
         </is>
       </c>
       <c r="B24">
-        <v>6.74</v>
+        <v>6.61</v>
+      </c>
+      <c r="C24">
+        <v>7.18</v>
+      </c>
+      <c r="D24">
+        <v>-0.5699999999999994</v>
+      </c>
+      <c r="E24">
+        <v>-7.938718662952637</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Requínoa</t>
+          <t>Coinco</t>
         </is>
       </c>
       <c r="B25">
-        <v>6.61</v>
+        <v>6.2</v>
+      </c>
+      <c r="C25">
+        <v>6.66</v>
+      </c>
+      <c r="D25">
+        <v>-0.46</v>
+      </c>
+      <c r="E25">
+        <v>-6.906906906906906</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Coinco</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B26">
         <v>6.2</v>
       </c>
+      <c r="C26">
+        <v>6.42</v>
+      </c>
+      <c r="D26">
+        <v>-0.2199999999999998</v>
+      </c>
+      <c r="E26">
+        <v>-3.426791277258567</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -641,6 +866,15 @@
       <c r="B27">
         <v>5.81</v>
       </c>
+      <c r="C27">
+        <v>5.88</v>
+      </c>
+      <c r="D27">
+        <v>-0.07000000000000028</v>
+      </c>
+      <c r="E27">
+        <v>-1.190476190476197</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -651,6 +885,15 @@
       <c r="B28">
         <v>5.73</v>
       </c>
+      <c r="C28">
+        <v>6.11</v>
+      </c>
+      <c r="D28">
+        <v>-0.3799999999999999</v>
+      </c>
+      <c r="E28">
+        <v>-6.219312602291327</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -661,6 +904,15 @@
       <c r="B29">
         <v>5.43</v>
       </c>
+      <c r="C29">
+        <v>5.67</v>
+      </c>
+      <c r="D29">
+        <v>-0.2400000000000002</v>
+      </c>
+      <c r="E29">
+        <v>-4.232804232804233</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -671,6 +923,15 @@
       <c r="B30">
         <v>5.29</v>
       </c>
+      <c r="C30">
+        <v>5.73</v>
+      </c>
+      <c r="D30">
+        <v>-0.4400000000000004</v>
+      </c>
+      <c r="E30">
+        <v>-7.678883071553233</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -681,6 +942,15 @@
       <c r="B31">
         <v>4.99</v>
       </c>
+      <c r="C31">
+        <v>5.08</v>
+      </c>
+      <c r="D31">
+        <v>-0.08999999999999986</v>
+      </c>
+      <c r="E31">
+        <v>-1.771653543307083</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -691,6 +961,15 @@
       <c r="B32">
         <v>4.91</v>
       </c>
+      <c r="C32">
+        <v>4.94</v>
+      </c>
+      <c r="D32">
+        <v>-0.03000000000000025</v>
+      </c>
+      <c r="E32">
+        <v>-0.6072874493927127</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -701,6 +980,15 @@
       <c r="B33">
         <v>4.36</v>
       </c>
+      <c r="C33">
+        <v>4.63</v>
+      </c>
+      <c r="D33">
+        <v>-0.2699999999999996</v>
+      </c>
+      <c r="E33">
+        <v>-5.831533477321804</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -710,6 +998,15 @@
       </c>
       <c r="B34">
         <v>3.21</v>
+      </c>
+      <c r="C34">
+        <v>3.34</v>
+      </c>
+      <c r="D34">
+        <v>-0.1299999999999999</v>
+      </c>
+      <c r="E34">
+        <v>-3.892215568862267</v>
       </c>
     </row>
   </sheetData>
@@ -719,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -867,200 +1164,190 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marchihue</t>
+          <t>Mostazal</t>
         </is>
       </c>
       <c r="B15">
-        <v>9.51</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mostazal</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="B16">
-        <v>5.29</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>Navidad</t>
         </is>
       </c>
       <c r="B17">
-        <v>8.130000000000001</v>
+        <v>7.16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Navidad</t>
+          <t>Olivar</t>
         </is>
       </c>
       <c r="B18">
-        <v>7.16</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Olivar</t>
+          <t>Palmilla</t>
         </is>
       </c>
       <c r="B19">
-        <v>7.19</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Palmilla</t>
+          <t>Paredones</t>
         </is>
       </c>
       <c r="B20">
-        <v>9.09</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Paredones</t>
+          <t>Peralillo</t>
         </is>
       </c>
       <c r="B21">
-        <v>8.85</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Peralillo</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="B22">
-        <v>7.29</v>
+        <v>8.35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Pichidegua</t>
         </is>
       </c>
       <c r="B23">
-        <v>8.35</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="B24">
-        <v>10.34</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>Placilla</t>
         </is>
       </c>
       <c r="B25">
-        <v>8.619999999999999</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Placilla</t>
+          <t>Pumanque</t>
         </is>
       </c>
       <c r="B26">
-        <v>11.13</v>
+        <v>7.13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pumanque</t>
+          <t>Quinta de Tilcoco</t>
         </is>
       </c>
       <c r="B27">
-        <v>7.13</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="B28">
-        <v>7.69</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="B29">
-        <v>4.36</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Requínoa</t>
         </is>
       </c>
       <c r="B30">
-        <v>5.73</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Requínoa</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="B31">
-        <v>6.61</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="B32">
-        <v>6.74</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="B33">
-        <v>7.26</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="B34">
         <v>8.56</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_o_higgins.xlsx
@@ -1016,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1025,330 +1025,236 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chépica</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>8.869999999999999</v>
+          <t>Marchigüe</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chimbarongo</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>7.6</v>
+          <t>Codegua</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Codegua</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>5.43</v>
+          <t>Coinco</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coinco</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>6.2</v>
+          <t>Coltauco</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coltauco</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>5.81</v>
+          <t>Graneros</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Doñihue</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>4.91</v>
+          <t>Malloa</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Graneros</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>4.99</v>
+          <t>Peumo</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>La Estrella</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>8.23</v>
+          <t>Pichidegua</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Las Cabras</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>9.039999999999999</v>
+          <t>Rancagua</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Litueche</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>12.89</v>
+          <t>Requínoa</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lolol</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>10</v>
+          <t>Mostazal</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machalí</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>3.21</v>
+          <t>San Vicente</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Malloa</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>7.32</v>
+          <t>Nancagua</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mostazal</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>5.29</v>
+          <t>Peralillo</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nancagua</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>8.130000000000001</v>
+          <t>Placilla</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Navidad</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>7.16</v>
+          <t>Pumanque</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Olivar</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>7.19</v>
+          <t>Paredones</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Palmilla</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>9.09</v>
+          <t>Pichilemu</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Paredones</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>8.85</v>
+          <t>Litueche</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Peralillo</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>7.29</v>
+          <t>Navidad</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Peumo</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>8.35</v>
+          <t>La Estrella</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>10.34</v>
+          <t>Doñihue</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>8.619999999999999</v>
+          <t>Olivar</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Placilla</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>11.13</v>
+          <t>Rengo</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pumanque</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>7.13</v>
+          <t>Santa Cruz</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>7.69</v>
+          <t>Palmilla</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rancagua</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>4.36</v>
+          <t>Quinta de Tilcoco</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rengo</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>5.73</v>
+          <t>Machalí</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Requínoa</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>6.61</v>
+          <t>Las Cabras</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>San Fernando</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>6.74</v>
+          <t>Chimbarongo</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>7.26</v>
+          <t>Lolol</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>8.56</v>
+          <t>Chépica</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>San Fernando</t>
+        </is>
       </c>
     </row>
   </sheetData>
